--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F2D36C-9EA7-4A29-9189-04E6D655D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -550,7 +553,9 @@
         <v>30</v>
       </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -573,7 +578,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C192DD-DECB-4C01-B582-30404AB1ADEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -510,7 +510,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="15">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="2"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC1FF9E-1AEE-4112-924A-292CA0D552AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -510,7 +510,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5E08CB-F62C-45A1-8A4B-FE280FE74666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,9 @@
         <v>30</v>
       </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CF21CC-6E2D-4155-89BD-93C2D0913720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>No Compila Ni se Puede Probrar</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -526,7 +529,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -547,10 +550,12 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -573,7 +578,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2DA02E-86DD-44EA-923B-6CC743FCF955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>3.7333333333333334</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="2"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.7333333333333334</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27580DB-4C87-426E-A50F-BD7A6A8AF6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>3.7333333333333334</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="2"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.7333333333333334</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E8077-ADB3-48D4-93B7-DAD5170A062C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Falla</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,9 @@
       <c r="D6" s="12">
         <v>0.5</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834C18D2-4F47-40D3-BD0B-CAC87F629863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>3.7333333333333334</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.7333333333333334</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE31D95-78DD-4792-B2D4-ED9D27CA7FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,9 @@
       <c r="D6" s="12">
         <v>0.5</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433900F9-B191-45BA-B1BD-57F4C68DC68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,9 @@
       <c r="D6" s="12">
         <v>0.5</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B15D8D4-56D2-480A-AADD-BC031B4DAE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>3.4666666666666668</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.4666666666666668</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428456F4-51D0-4492-AF44-0037DD3FB4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,9 @@
       <c r="D6" s="12">
         <v>0.5</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Backend Development\Repository\Exams\Exam-03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE6F4E0-41D4-49D6-A4C5-BA527B302327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A98B7B-0F51-434B-AC35-0BB427D3D1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -510,7 +510,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -573,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E8077-ADB3-48D4-93B7-DAD5170A062C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAC67E5-0818-47DF-BB2F-301773D19A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
-  </si>
-  <si>
-    <t>Falla</t>
   </si>
 </sst>
 </file>
@@ -513,7 +510,7 @@
         <v>0.5</v>
       </c>
       <c r="D2" s="12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -529,7 +526,7 @@
       </c>
       <c r="D3" s="13">
         <f>(C5*C3)/30</f>
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E3" s="8"/>
     </row>
@@ -550,7 +547,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="15">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="2"/>
@@ -566,9 +563,7 @@
       <c r="D6" s="12">
         <v>0.5</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
@@ -578,7 +573,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="7"/>
     </row>

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F2D36C-9EA7-4A29-9189-04E6D655D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF940451-16A8-43C7-A237-CB86CEBF3026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Creterio</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Hay Codigos Repetidos</t>
+  </si>
+  <si>
+    <t>Hay Combinacion de Ingles y espa;ol</t>
+  </si>
+  <si>
+    <t>Hay Else Innecesarios</t>
   </si>
 </sst>
 </file>
@@ -477,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -566,7 +575,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -578,13 +587,26 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5E08CB-F62C-45A1-8A4B-FE280FE74666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD87459-DD73-425E-B4AB-2153A153FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Creterio</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Existen variables declaradas , asignadas y nunca usadas</t>
+  </si>
+  <si>
+    <t>Existen else innecesarios</t>
+  </si>
+  <si>
+    <t>existen funciones con muchas responsabilidades</t>
   </si>
 </sst>
 </file>
@@ -477,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -566,7 +575,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -578,13 +587,28 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2DA02E-86DD-44EA-923B-6CC743FCF955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABFB468-43A6-4756-A4D1-F49EBD47E5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Funciones con demasiadas responsabilidades</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -561,7 +564,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -573,13 +576,18 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>4.7333333333333334</v>
+        <v>4.6333333333333337</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27580DB-4C87-426E-A50F-BD7A6A8AF6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB8D8A-5A7A-40D8-B20E-B376E3B4BCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Funciones con muchas responsabilidades</t>
+  </si>
+  <si>
+    <t>Los objetos DTO no deben tener logica asociada</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -561,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -573,13 +579,23 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>4.7333333333333334</v>
+        <v>4.5333333333333332</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAC67E5-0818-47DF-BB2F-301773D19A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835D329B-8A0C-4E09-B30F-CB4800013F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Funciones con muhcas responsabiolidades</t>
+  </si>
+  <si>
+    <t>Else Innecesarios</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -561,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -573,13 +579,23 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834C18D2-4F47-40D3-BD0B-CAC87F629863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B6478C-0D88-40A1-9647-C4EB66D8BD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Hay Funciones con mas de una responsabilidad</t>
+  </si>
+  <si>
+    <t>Los DTO no deben tener logica asociada, son solo objetos de conversion o transporte</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -561,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -573,13 +579,23 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>4.7333333333333334</v>
+        <v>4.5333333333333332</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE31D95-78DD-4792-B2D4-ED9D27CA7FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159ED375-2810-4896-BB72-8618CE337899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Creterio</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Hay Logica de Funciones Innecesarias *AddSpaces… ???</t>
+  </si>
+  <si>
+    <t>Hay Funciones con multiples responsabilidades (LoadIssuingNetworkData)</t>
   </si>
 </sst>
 </file>
@@ -477,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -564,7 +570,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
@@ -578,13 +584,23 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433900F9-B191-45BA-B1BD-57F4C68DC68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928E8CE0-15A0-4F27-8F4C-01FA9A534984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Creterio</t>
   </si>
@@ -61,6 +61,18 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Existen Funciones con multiples responsabilidades</t>
+  </si>
+  <si>
+    <t>Funcion  AddSpaceBetweenLowerAndCapitalLetterNo es Necesaria Usa lo Simple =&gt;CreditCardResult("Not Found", false);</t>
+  </si>
+  <si>
+    <t>Utiliza Logica Difusa o Logica inversa para evitar If como este if (creditCardNumber.Length &lt; numberLength) { continue; }</t>
+  </si>
+  <si>
+    <t>puedes retornas las operaciones boleanas directametne (rewturn initalCreditCardDigits == number)</t>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -564,7 +576,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
@@ -578,13 +590,33 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B15D8D4-56D2-480A-AADD-BC031B4DAE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E25527F-6D29-4739-9B71-42CDC36F8513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Creterio</t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t>Cumple con Clean Code</t>
+  </si>
+  <si>
+    <t>Hay Funciones con mas de una responsabilidad</t>
+  </si>
+  <si>
+    <t>Existen else Innecesarios</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -561,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -573,13 +579,23 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>4.4666666666666668</v>
+        <v>4.2666666666666666</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">

--- a/Exams/Exam-01/Program_CheckList.xlsx
+++ b/Exams/Exam-01/Program_CheckList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Dropbox\Personal\Cursos\Services Development\Repository\Exams\Exam-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428456F4-51D0-4492-AF44-0037DD3FB4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30A2362-DD00-425E-BD38-2C571A72DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Creterio</t>
   </si>
@@ -61,6 +61,18 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Funciones con multiples responsabilidades</t>
+  </si>
+  <si>
+    <t>Else Innecesarios</t>
+  </si>
+  <si>
+    <t>Usa Logica inversa para evitar if con contuinue</t>
+  </si>
+  <si>
+    <t>retorna las cdiciones booleans en lugar del valor</t>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" bestFit="1" customWidth="1"/>
@@ -564,7 +576,7 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="12">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
@@ -578,13 +590,33 @@
       <c r="C7" s="7"/>
       <c r="D7" s="14">
         <f>SUM(D2:D6)</f>
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
